--- a/annual/Predicted_Annual_Jevons_Index_With_Error_Results.xlsx
+++ b/annual/Predicted_Annual_Jevons_Index_With_Error_Results.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="Predicted_Prices" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Adjacent Predicted Years" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Model_Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Summary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6319,6 +6320,138 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Samples</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>R2_Score</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Uses_Error_Feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.7210931761793971</v>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>47</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.8848512296779283</v>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>86</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.6014481980898134</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>118</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.7796812255151336</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>142</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.741432205830449</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>148</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.8099932091830554</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/annual/Predicted_Annual_Jevons_Index_With_Error_Results.xlsx
+++ b/annual/Predicted_Annual_Jevons_Index_With_Error_Results.xlsx
@@ -10,7 +10,8 @@
     <sheet name="Predicted_Prices" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Adjacent Predicted Years" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Model_Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Price_Change_R2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Summary" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6452,6 +6453,115 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>R2_Price_Change</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Samples</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2020 → 2021</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.237441708177539</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2021 → 2022</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.1276362718584013</v>
+      </c>
+      <c r="C3" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2022 → 2023</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.004481314914410617</v>
+      </c>
+      <c r="C4" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2023 → 2024</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.09262072812606381</v>
+      </c>
+      <c r="C5" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2024 → 2025</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.04391774245696434</v>
+      </c>
+      <c r="C6" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Overall (Average)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.1012195531066758</v>
+      </c>
+      <c r="C7" t="n">
+        <v>413</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
